--- a/artfynd/A 5338-2023 artfynd.xlsx
+++ b/artfynd/A 5338-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5338-2023 artfynd.xlsx
+++ b/artfynd/A 5338-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3489,126 +3489,6 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>113349422</v>
-      </c>
-      <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Sågarstugan, Ög</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>569110</v>
-      </c>
-      <c r="R27" t="n">
-        <v>6517375</v>
-      </c>
-      <c r="S27" t="n">
-        <v>15</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Simonstorp</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>E-Nor-0735</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2023-02-17</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2023-02-17</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Marika Sjödin</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
